--- a/assets/libreoffice_calc_njc/4f989467-8112-445d-8f1d-d0b905bd6d74/EmpStats_L2_07.xlsx
+++ b/assets/libreoffice_calc_njc/4f989467-8112-445d-8f1d-d0b905bd6d74/EmpStats_L2_07.xlsx
@@ -282,8 +282,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -305,53 +309,55 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="0" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="B2" s="1" t="n">
+        <f aca="false">COUNTA(employees A2:A16)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="0" t="n">
-        <v>84933.33</v>
+      <c r="B3" s="1" t="e">
+        <f aca="false">ROUND(AVERAGE($'employees' F2:F16), 2)</f>
+        <v>#NAME?</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="1" t="n">
         <v>62000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <v>125000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="1" t="n">
         <v>1274000</v>
       </c>
     </row>
@@ -372,373 +378,373 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>1001</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="E2" s="1" t="n">
         <v>95000</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="0" t="n">
+      <c r="G2" s="1" t="n">
         <v>4.5</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>1002</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="0" t="n">
+      <c r="E3" s="1" t="n">
         <v>85000</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="0" t="n">
+      <c r="G3" s="1" t="n">
         <v>3.8</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>1003</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4" s="1" t="n">
         <v>110000</v>
       </c>
-      <c r="F4" s="0" t="s">
+      <c r="F4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="0" t="n">
+      <c r="G4" s="1" t="n">
         <v>4.8</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>1004</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5" s="1" t="n">
         <v>65000</v>
       </c>
-      <c r="F5" s="0" t="s">
+      <c r="F5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G5" s="0" t="n">
+      <c r="G5" s="1" t="n">
         <v>3.2</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>1005</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="E6" s="1" t="n">
         <v>72000</v>
       </c>
-      <c r="F6" s="0" t="s">
+      <c r="F6" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="0" t="n">
+      <c r="G6" s="1" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>1006</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7" s="1" t="n">
         <v>68000</v>
       </c>
-      <c r="F7" s="0" t="s">
+      <c r="F7" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G7" s="0" t="n">
+      <c r="G7" s="1" t="n">
         <v>3.5</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="1" t="n">
         <v>1007</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E8" s="0" t="n">
+      <c r="E8" s="1" t="n">
         <v>90000</v>
       </c>
-      <c r="F8" s="0" t="s">
+      <c r="F8" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G8" s="0" t="n">
+      <c r="G8" s="1" t="n">
         <v>4.2</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="1" t="n">
         <v>1008</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="0" t="n">
+      <c r="E9" s="1" t="n">
         <v>62000</v>
       </c>
-      <c r="F9" s="0" t="s">
+      <c r="F9" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G9" s="0" t="n">
+      <c r="G9" s="1" t="n">
         <v>3.9</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+      <c r="A10" s="1" t="n">
         <v>1009</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="0" t="n">
+      <c r="E10" s="1" t="n">
         <v>125000</v>
       </c>
-      <c r="F10" s="0" t="s">
+      <c r="F10" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="G10" s="0" t="n">
+      <c r="G10" s="1" t="n">
         <v>4.9</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+      <c r="A11" s="1" t="n">
         <v>1010</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E11" s="0" t="n">
+      <c r="E11" s="1" t="n">
         <v>115000</v>
       </c>
-      <c r="F11" s="0" t="s">
+      <c r="F11" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G11" s="0" t="n">
+      <c r="G11" s="1" t="n">
         <v>4.1</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
+      <c r="A12" s="1" t="n">
         <v>1011</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E12" s="0" t="n">
+      <c r="E12" s="1" t="n">
         <v>63000</v>
       </c>
-      <c r="F12" s="0" t="s">
+      <c r="F12" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="G12" s="0" t="n">
+      <c r="G12" s="1" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
+      <c r="A13" s="1" t="n">
         <v>1012</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="D13" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="0" t="n">
+      <c r="E13" s="1" t="n">
         <v>88000</v>
       </c>
-      <c r="F13" s="0" t="s">
+      <c r="F13" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="G13" s="0" t="n">
+      <c r="G13" s="1" t="n">
         <v>4.3</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
+      <c r="A14" s="1" t="n">
         <v>1013</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="D14" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E14" s="0" t="n">
+      <c r="E14" s="1" t="n">
         <v>82000</v>
       </c>
-      <c r="F14" s="0" t="s">
+      <c r="F14" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G14" s="0" t="n">
+      <c r="G14" s="1" t="n">
         <v>3.7</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="n">
+      <c r="A15" s="1" t="n">
         <v>1014</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="C15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="0" t="s">
+      <c r="D15" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E15" s="0" t="n">
+      <c r="E15" s="1" t="n">
         <v>78000</v>
       </c>
-      <c r="F15" s="0" t="s">
+      <c r="F15" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="G15" s="0" t="n">
+      <c r="G15" s="1" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="n">
+      <c r="A16" s="1" t="n">
         <v>1015</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C16" s="0" t="s">
+      <c r="C16" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D16" s="0" t="s">
+      <c r="D16" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E16" s="0" t="n">
+      <c r="E16" s="1" t="n">
         <v>76000</v>
       </c>
-      <c r="F16" s="0" t="s">
+      <c r="F16" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="G16" s="0" t="n">
+      <c r="G16" s="1" t="n">
         <v>3.6</v>
       </c>
     </row>

--- a/assets/libreoffice_calc_njc/4f989467-8112-445d-8f1d-d0b905bd6d74/EmpStats_L2_07.xlsx
+++ b/assets/libreoffice_calc_njc/4f989467-8112-445d-8f1d-d0b905bd6d74/EmpStats_L2_07.xlsx
@@ -309,7 +309,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.16015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -324,40 +324,43 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="n">
-        <f aca="false">COUNTA(employees A2:A16)</f>
-        <v>1</v>
+        <f aca="false">COUNTA(Employees!A2:A16)</f>
+        <v>15</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="1" t="e">
-        <f aca="false">ROUND(AVERAGE($'employees' F2:F16), 2)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(Employees!E2:E16), 2)</f>
+        <v>84933.33</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="1" t="n">
+        <f aca="false">MIN(Employees!E2:E16)</f>
         <v>62000</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="1" t="n">
+        <f aca="false">MAX(Employees!E2:E16)</f>
         <v>125000</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="1" t="n">
+        <f aca="false">SUM(Employees!E2:E16)</f>
         <v>1274000</v>
       </c>
     </row>

--- a/assets/libreoffice_calc_njc/4f989467-8112-445d-8f1d-d0b905bd6d74/EmpStats_L2_07.xlsx
+++ b/assets/libreoffice_calc_njc/4f989467-8112-445d-8f1d-d0b905bd6d74/EmpStats_L2_07.xlsx
@@ -10,6 +10,7 @@
   <sheets>
     <sheet name="Stats" sheetId="1" state="visible" r:id="rId2"/>
     <sheet name="Employees" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -309,9 +310,9 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultColWidth="9.16015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.171875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -324,7 +325,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="n">
-        <f aca="false">COUNTA(Employees!A2:A16)</f>
+        <f aca="false">COUNTA(Employees!A2:A1000)</f>
         <v>15</v>
       </c>
     </row>
@@ -333,7 +334,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(Employees!E2:E16), 2)</f>
+        <f aca="false">ROUND(AVERAGE(Employees!E2:E16),2)</f>
         <v>84933.33</v>
       </c>
     </row>
@@ -760,4 +761,22 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>